--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/11.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/11.xlsx
@@ -426,13 +426,13 @@
         <v>-5.05360304681277</v>
       </c>
       <c r="E2">
-        <v>-10.05362734380545</v>
+        <v>-13.03338618770561</v>
       </c>
       <c r="F2">
-        <v>-3.817992723692389</v>
+        <v>-3.950804869383234</v>
       </c>
       <c r="G2">
-        <v>-9.292236010742171</v>
+        <v>-8.461420064884486</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.651673122500095</v>
       </c>
       <c r="E3">
-        <v>-12.21325570060304</v>
+        <v>-13.06593490485829</v>
       </c>
       <c r="F3">
-        <v>-3.195856497861251</v>
+        <v>-3.920007826081954</v>
       </c>
       <c r="G3">
-        <v>-9.941943298942032</v>
+        <v>-8.14490252826398</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.267687228481112</v>
       </c>
       <c r="E4">
-        <v>-11.13247797717689</v>
+        <v>-13.97527221800685</v>
       </c>
       <c r="F4">
-        <v>-4.009502155178204</v>
+        <v>-4.07478496182543</v>
       </c>
       <c r="G4">
-        <v>-9.248721425269791</v>
+        <v>-8.58732713890781</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.796659161955358</v>
       </c>
       <c r="E5">
-        <v>-12.43950188752308</v>
+        <v>-14.89263353543498</v>
       </c>
       <c r="F5">
-        <v>-3.170590463708463</v>
+        <v>-4.037029632340634</v>
       </c>
       <c r="G5">
-        <v>-8.613036446268799</v>
+        <v>-7.889174874075251</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.238549192762117</v>
       </c>
       <c r="E6">
-        <v>-15.72150653237631</v>
+        <v>-14.47828425440214</v>
       </c>
       <c r="F6">
-        <v>-3.578088411800221</v>
+        <v>-3.809018191250459</v>
       </c>
       <c r="G6">
-        <v>-9.085997631022586</v>
+        <v>-7.973843931909646</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.57700277354114</v>
       </c>
       <c r="E7">
-        <v>-13.6204218424135</v>
+        <v>-15.24371279514539</v>
       </c>
       <c r="F7">
-        <v>-3.351694772247714</v>
+        <v>-3.504980018298748</v>
       </c>
       <c r="G7">
-        <v>-9.207852829440503</v>
+        <v>-8.161129611270043</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.808524180992785</v>
       </c>
       <c r="E8">
-        <v>-14.92696398024601</v>
+        <v>-16.06441227219945</v>
       </c>
       <c r="F8">
-        <v>-4.051861550687759</v>
+        <v>-3.407448868660537</v>
       </c>
       <c r="G8">
-        <v>-9.235021543027923</v>
+        <v>-7.887049727978085</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.944012015237869</v>
       </c>
       <c r="E9">
-        <v>-15.78634231436821</v>
+        <v>-16.47133561138351</v>
       </c>
       <c r="F9">
-        <v>-3.067555641046052</v>
+        <v>-3.411824305282124</v>
       </c>
       <c r="G9">
-        <v>-8.900992437062525</v>
+        <v>-7.776579986722012</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.990366240614561</v>
       </c>
       <c r="E10">
-        <v>-15.25369711517027</v>
+        <v>-17.61386743399854</v>
       </c>
       <c r="F10">
-        <v>-2.834076146729998</v>
+        <v>-3.32613715276914</v>
       </c>
       <c r="G10">
-        <v>-7.851458752339733</v>
+        <v>-7.432114429253639</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.960208414423054</v>
       </c>
       <c r="E11">
-        <v>-16.67684481415867</v>
+        <v>-17.7153303866641</v>
       </c>
       <c r="F11">
-        <v>-3.18580757289789</v>
+        <v>-3.151875158977014</v>
       </c>
       <c r="G11">
-        <v>-7.90527141985176</v>
+        <v>-7.071857783125917</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.868956542102238</v>
       </c>
       <c r="E12">
-        <v>-16.60858678603512</v>
+        <v>-18.97205475465529</v>
       </c>
       <c r="F12">
-        <v>-2.660408092365679</v>
+        <v>-2.931286718183325</v>
       </c>
       <c r="G12">
-        <v>-7.557095994319415</v>
+        <v>-6.348746800002314</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.72035169883376</v>
       </c>
       <c r="E13">
-        <v>-17.9847948906303</v>
+        <v>-19.69435634900152</v>
       </c>
       <c r="F13">
-        <v>-2.07704608792478</v>
+        <v>-3.090643068929477</v>
       </c>
       <c r="G13">
-        <v>-8.006758894342108</v>
+        <v>-6.20453710102299</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.531963203260153</v>
       </c>
       <c r="E14">
-        <v>-17.60679036190103</v>
+        <v>-20.7202369251361</v>
       </c>
       <c r="F14">
-        <v>-2.256788560453828</v>
+        <v>-2.785210753638855</v>
       </c>
       <c r="G14">
-        <v>-7.37102561656618</v>
+        <v>-5.818099908135584</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.304033013457526</v>
       </c>
       <c r="E15">
-        <v>-19.12532901859809</v>
+        <v>-20.68658760698234</v>
       </c>
       <c r="F15">
-        <v>-2.041503327772861</v>
+        <v>-2.553555324343765</v>
       </c>
       <c r="G15">
-        <v>-7.256708943155102</v>
+        <v>-5.645185072376969</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.042588337850596</v>
       </c>
       <c r="E16">
-        <v>-20.33777184744396</v>
+        <v>-22.21668465079639</v>
       </c>
       <c r="F16">
-        <v>-1.859678339593176</v>
+        <v>-1.991228053362154</v>
       </c>
       <c r="G16">
-        <v>-6.663952437465786</v>
+        <v>-5.467586560821896</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.748173475271202</v>
       </c>
       <c r="E17">
-        <v>-21.52586439829236</v>
+        <v>-23.5142101668427</v>
       </c>
       <c r="F17">
-        <v>-1.111918540392687</v>
+        <v>-1.781519390036834</v>
       </c>
       <c r="G17">
-        <v>-6.137172058338494</v>
+        <v>-4.777658141451344</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.413518206246253</v>
       </c>
       <c r="E18">
-        <v>-22.43264333326483</v>
+        <v>-23.8794394175368</v>
       </c>
       <c r="F18">
-        <v>-1.198960073609248</v>
+        <v>-1.555042913744046</v>
       </c>
       <c r="G18">
-        <v>-6.298351597160055</v>
+        <v>-4.594564012531978</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.043697852289246</v>
       </c>
       <c r="E19">
-        <v>-22.75955505627606</v>
+        <v>-25.53304881293993</v>
       </c>
       <c r="F19">
-        <v>-0.8862414386436008</v>
+        <v>-1.173668360066973</v>
       </c>
       <c r="G19">
-        <v>-5.887796345739944</v>
+        <v>-4.381803992823792</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.63109131716593</v>
       </c>
       <c r="E20">
-        <v>-23.2375523008619</v>
+        <v>-25.25867936639911</v>
       </c>
       <c r="F20">
-        <v>-0.6463412685884472</v>
+        <v>-0.8419353797374665</v>
       </c>
       <c r="G20">
-        <v>-6.084557722593788</v>
+        <v>-4.115800447924442</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.180773194365739</v>
       </c>
       <c r="E21">
-        <v>-24.363936437846</v>
+        <v>-26.4629112964558</v>
       </c>
       <c r="F21">
-        <v>0.08207698012407566</v>
+        <v>-0.668384125176942</v>
       </c>
       <c r="G21">
-        <v>-6.147912661586334</v>
+        <v>-3.784027025285765</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.696478211814699</v>
       </c>
       <c r="E22">
-        <v>-24.54919873541262</v>
+        <v>-27.23157934203241</v>
       </c>
       <c r="F22">
-        <v>-0.2132103195844613</v>
+        <v>-0.5191827304217091</v>
       </c>
       <c r="G22">
-        <v>-5.997588598774622</v>
+        <v>-4.132699797662718</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.181965751708659</v>
       </c>
       <c r="E23">
-        <v>-26.21612332632316</v>
+        <v>-26.8164492572705</v>
       </c>
       <c r="F23">
-        <v>0.544107182709528</v>
+        <v>-0.2950844969423588</v>
       </c>
       <c r="G23">
-        <v>-5.904575601227029</v>
+        <v>-3.890963123737765</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.652538452731716</v>
       </c>
       <c r="E24">
-        <v>-25.81790511807595</v>
+        <v>-27.76163709057498</v>
       </c>
       <c r="F24">
-        <v>0.287983437070546</v>
+        <v>-0.3336474846448843</v>
       </c>
       <c r="G24">
-        <v>-5.43157394993208</v>
+        <v>-4.307196744643547</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.114714697855649</v>
       </c>
       <c r="E25">
-        <v>-26.19069321338123</v>
+        <v>-27.99265116409592</v>
       </c>
       <c r="F25">
-        <v>0.3923386773730193</v>
+        <v>-0.4391533272698461</v>
       </c>
       <c r="G25">
-        <v>-6.332048477597554</v>
+        <v>-3.83438828844834</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.586170846101195</v>
       </c>
       <c r="E26">
-        <v>-26.43964085340278</v>
+        <v>-28.22466200833481</v>
       </c>
       <c r="F26">
-        <v>0.6611347875400281</v>
+        <v>-0.820956975261569</v>
       </c>
       <c r="G26">
-        <v>-5.783418776987235</v>
+        <v>-3.539974620908495</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.079719476735423</v>
       </c>
       <c r="E27">
-        <v>-25.60504888446716</v>
+        <v>-28.83353940139998</v>
       </c>
       <c r="F27">
-        <v>-0.2331043911300942</v>
+        <v>-0.4840177058054673</v>
       </c>
       <c r="G27">
-        <v>-5.259223035005145</v>
+        <v>-3.673548146423624</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.607642024635272</v>
       </c>
       <c r="E28">
-        <v>-26.67642373745391</v>
+        <v>-27.82765238458313</v>
       </c>
       <c r="F28">
-        <v>0.04351067895193908</v>
+        <v>-0.7952386525068528</v>
       </c>
       <c r="G28">
-        <v>-4.895898763982864</v>
+        <v>-3.778842086527814</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.187761587488244</v>
       </c>
       <c r="E29">
-        <v>-26.91698604381062</v>
+        <v>-28.17758743457355</v>
       </c>
       <c r="F29">
-        <v>0.02296551062770574</v>
+        <v>-0.9147927779158914</v>
       </c>
       <c r="G29">
-        <v>-5.31891771008095</v>
+        <v>-3.481097108889708</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.8274615339067971</v>
       </c>
       <c r="E30">
-        <v>-25.77042145299918</v>
+        <v>-28.46832468694552</v>
       </c>
       <c r="F30">
-        <v>-0.2733671887431642</v>
+        <v>-1.010239755168659</v>
       </c>
       <c r="G30">
-        <v>-4.641499978791012</v>
+        <v>-3.332689332607873</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.5412365366605896</v>
       </c>
       <c r="E31">
-        <v>-24.5564876212877</v>
+        <v>-27.62589353163428</v>
       </c>
       <c r="F31">
-        <v>-0.2080736133197016</v>
+        <v>-1.025670583148008</v>
       </c>
       <c r="G31">
-        <v>-4.979160630482649</v>
+        <v>-3.343529144150176</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.3350682559661991</v>
       </c>
       <c r="E32">
-        <v>-25.86862828798608</v>
+        <v>-27.03855053928836</v>
       </c>
       <c r="F32">
-        <v>-0.06402714891208994</v>
+        <v>-1.392173456842621</v>
       </c>
       <c r="G32">
-        <v>-5.268673930424975</v>
+        <v>-3.512885535031104</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.2123207441119325</v>
       </c>
       <c r="E33">
-        <v>-24.11486835469603</v>
+        <v>-27.17889585637696</v>
       </c>
       <c r="F33">
-        <v>0.3065280981170185</v>
+        <v>-1.255698270496597</v>
       </c>
       <c r="G33">
-        <v>-4.504563814242529</v>
+        <v>-2.956650735426871</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.1733504654743063</v>
       </c>
       <c r="E34">
-        <v>-25.16984632937235</v>
+        <v>-27.4268882577938</v>
       </c>
       <c r="F34">
-        <v>-0.3343391714262218</v>
+        <v>-1.170771559259383</v>
       </c>
       <c r="G34">
-        <v>-4.239983125145335</v>
+        <v>-2.907182346914457</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.2040779302973054</v>
       </c>
       <c r="E35">
-        <v>-24.78163736041798</v>
+        <v>-27.56956352643563</v>
       </c>
       <c r="F35">
-        <v>-0.2595657594451216</v>
+        <v>-0.9771655298770829</v>
       </c>
       <c r="G35">
-        <v>-3.926020202107234</v>
+        <v>-3.139778804025922</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.2927923138694888</v>
       </c>
       <c r="E36">
-        <v>-24.51822823856338</v>
+        <v>-26.7576190188543</v>
       </c>
       <c r="F36">
-        <v>-0.160087118042929</v>
+        <v>-0.8943743498042863</v>
       </c>
       <c r="G36">
-        <v>-4.856205003219578</v>
+        <v>-3.052506833834187</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.421145828346392</v>
       </c>
       <c r="E37">
-        <v>-23.97888806270982</v>
+        <v>-25.80602693368694</v>
       </c>
       <c r="F37">
-        <v>-0.5399374756988508</v>
+        <v>-1.221388121040044</v>
       </c>
       <c r="G37">
-        <v>-4.433700373805942</v>
+        <v>-3.247769643292731</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.574403798062293</v>
       </c>
       <c r="E38">
-        <v>-24.3565271088425</v>
+        <v>-25.5749962473207</v>
       </c>
       <c r="F38">
-        <v>-0.08320882449131529</v>
+        <v>-0.6468979314831285</v>
       </c>
       <c r="G38">
-        <v>-4.337387395095181</v>
+        <v>-2.816487690563772</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.7416527690792003</v>
       </c>
       <c r="E39">
-        <v>-23.19860763826898</v>
+        <v>-25.19119383558197</v>
       </c>
       <c r="F39">
-        <v>-0.02418764704185052</v>
+        <v>-0.5543875166732852</v>
       </c>
       <c r="G39">
-        <v>-4.270557555051863</v>
+        <v>-2.673494598563907</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.9111051452531179</v>
       </c>
       <c r="E40">
-        <v>-21.41399349804678</v>
+        <v>-25.12562293518558</v>
       </c>
       <c r="F40">
-        <v>0.2901595582377003</v>
+        <v>-0.2716798043436616</v>
       </c>
       <c r="G40">
-        <v>-4.534626538209199</v>
+        <v>-2.97022399655607</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.079154251130601</v>
       </c>
       <c r="E41">
-        <v>-22.11123876847032</v>
+        <v>-24.62560951736682</v>
       </c>
       <c r="F41">
-        <v>0.1872465055835009</v>
+        <v>-0.08461207887165766</v>
       </c>
       <c r="G41">
-        <v>-3.629327354539347</v>
+        <v>-2.968814194476868</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.240909085414803</v>
       </c>
       <c r="E42">
-        <v>-22.59041137186109</v>
+        <v>-24.17761507139154</v>
       </c>
       <c r="F42">
-        <v>0.5069110012216217</v>
+        <v>-0.1488296050388837</v>
       </c>
       <c r="G42">
-        <v>-4.352172041714656</v>
+        <v>-2.794178878032709</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.395632290796357</v>
       </c>
       <c r="E43">
-        <v>-22.74265563939533</v>
+        <v>-24.19875491703492</v>
       </c>
       <c r="F43">
-        <v>-0.05006584470530707</v>
+        <v>-0.1700399523875651</v>
       </c>
       <c r="G43">
-        <v>-4.819852995532917</v>
+        <v>-2.99914060364724</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.543994718283208</v>
       </c>
       <c r="E44">
-        <v>-20.60093177661907</v>
+        <v>-23.52611742371099</v>
       </c>
       <c r="F44">
-        <v>0.7701620199942906</v>
+        <v>0.02233677976898092</v>
       </c>
       <c r="G44">
-        <v>-4.446639223999499</v>
+        <v>-3.226170953290451</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.684859239794209</v>
       </c>
       <c r="E45">
-        <v>-20.75509067457406</v>
+        <v>-22.4084176516071</v>
       </c>
       <c r="F45">
-        <v>0.4091719313653081</v>
+        <v>0.08575327465769987</v>
       </c>
       <c r="G45">
-        <v>-4.176938864759133</v>
+        <v>-2.87121672942728</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.820887465191595</v>
       </c>
       <c r="E46">
-        <v>-19.9056385155182</v>
+        <v>-21.94757732300413</v>
       </c>
       <c r="F46">
-        <v>0.2651627434908224</v>
+        <v>0.2947967589585719</v>
       </c>
       <c r="G46">
-        <v>-4.036342436293909</v>
+        <v>-3.428025892841557</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.950500212287967</v>
       </c>
       <c r="E47">
-        <v>-19.76003938610369</v>
+        <v>-21.49921324122094</v>
       </c>
       <c r="F47">
-        <v>0.286644795347622</v>
+        <v>0.3771364787968428</v>
       </c>
       <c r="G47">
-        <v>-4.170396338813802</v>
+        <v>-3.443209983383472</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.074150651008169</v>
       </c>
       <c r="E48">
-        <v>-18.27454783191829</v>
+        <v>-21.46144393743295</v>
       </c>
       <c r="F48">
-        <v>-0.2317839734900318</v>
+        <v>0.3242236825756216</v>
       </c>
       <c r="G48">
-        <v>-3.830667977406004</v>
+        <v>-3.190630887171626</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.191183407691617</v>
       </c>
       <c r="E49">
-        <v>-17.65152875429208</v>
+        <v>-20.70150594206112</v>
       </c>
       <c r="F49">
-        <v>0.1294687076056382</v>
+        <v>0.3529845988008204</v>
       </c>
       <c r="G49">
-        <v>-3.81797192645942</v>
+        <v>-3.013343054222896</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.29824717072874</v>
       </c>
       <c r="E50">
-        <v>-17.93868178529073</v>
+        <v>-20.38452039411623</v>
       </c>
       <c r="F50">
-        <v>-0.1085402996689242</v>
+        <v>0.4280437975358864</v>
       </c>
       <c r="G50">
-        <v>-3.881324254707375</v>
+        <v>-2.944205315961034</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.396013147261833</v>
       </c>
       <c r="E51">
-        <v>-16.83984589902422</v>
+        <v>-20.21739517040513</v>
       </c>
       <c r="F51">
-        <v>-0.01861273442100984</v>
+        <v>0.3690234484538244</v>
       </c>
       <c r="G51">
-        <v>-4.546667292263414</v>
+        <v>-2.585556888501438</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.480282451408585</v>
       </c>
       <c r="E52">
-        <v>-17.39409610353391</v>
+        <v>-19.38568553012894</v>
       </c>
       <c r="F52">
-        <v>0.4029103021675466</v>
+        <v>0.4404038675530578</v>
       </c>
       <c r="G52">
-        <v>-4.419675453862481</v>
+        <v>-3.219281198314504</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.551324713184343</v>
       </c>
       <c r="E53">
-        <v>-16.99430382819459</v>
+        <v>-18.84424798255634</v>
       </c>
       <c r="F53">
-        <v>0.1069835028240484</v>
+        <v>0.3076571628870342</v>
       </c>
       <c r="G53">
-        <v>-4.709684795277118</v>
+        <v>-2.97986286558646</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.608096415556709</v>
       </c>
       <c r="E54">
-        <v>-17.3017743689943</v>
+        <v>-18.89435232397907</v>
       </c>
       <c r="F54">
-        <v>-0.007365990193200956</v>
+        <v>0.4563549102613651</v>
       </c>
       <c r="G54">
-        <v>-4.673810553850631</v>
+        <v>-2.718289754258228</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.648562958036867</v>
       </c>
       <c r="E55">
-        <v>-15.1319581848169</v>
+        <v>-19.04790069986931</v>
       </c>
       <c r="F55">
-        <v>-0.001463044080851679</v>
+        <v>0.4167846277970355</v>
       </c>
       <c r="G55">
-        <v>-4.733408631376565</v>
+        <v>-3.24133937936482</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.675132525115453</v>
       </c>
       <c r="E56">
-        <v>-15.79419603698346</v>
+        <v>-18.0035632526072</v>
       </c>
       <c r="F56">
-        <v>0.395521264934575</v>
+        <v>0.3724802256257068</v>
       </c>
       <c r="G56">
-        <v>-5.150354985555721</v>
+        <v>-2.782012808238121</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.684835780339309</v>
       </c>
       <c r="E57">
-        <v>-15.0471496095639</v>
+        <v>-18.05471420328379</v>
       </c>
       <c r="F57">
-        <v>0.3095914007725711</v>
+        <v>0.6991560229611226</v>
       </c>
       <c r="G57">
-        <v>-3.759300663263331</v>
+        <v>-3.015885919454641</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.679108923406846</v>
       </c>
       <c r="E58">
-        <v>-15.90529859313395</v>
+        <v>-17.6754014129872</v>
       </c>
       <c r="F58">
-        <v>0.07072089139909724</v>
+        <v>0.685986637991416</v>
       </c>
       <c r="G58">
-        <v>-4.732103259081008</v>
+        <v>-3.075648473889815</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.655915691047732</v>
       </c>
       <c r="E59">
-        <v>-14.55828756415231</v>
+        <v>-17.16944059655129</v>
       </c>
       <c r="F59">
-        <v>0.2566554102640715</v>
+        <v>0.5978616002119934</v>
       </c>
       <c r="G59">
-        <v>-4.917701092063251</v>
+        <v>-3.375599530707412</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.612397942795295</v>
       </c>
       <c r="E60">
-        <v>-13.65097286491894</v>
+        <v>-17.04486086965173</v>
       </c>
       <c r="F60">
-        <v>0.179329798314946</v>
+        <v>0.6178691580918099</v>
       </c>
       <c r="G60">
-        <v>-4.249695095024277</v>
+        <v>-3.025960782831747</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.549443876220618</v>
       </c>
       <c r="E61">
-        <v>-14.30572663027816</v>
+        <v>-17.22392242271039</v>
       </c>
       <c r="F61">
-        <v>0.3665176370603559</v>
+        <v>0.6660262970535592</v>
       </c>
       <c r="G61">
-        <v>-4.933590083644767</v>
+        <v>-3.007534147507669</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.463894523247666</v>
       </c>
       <c r="E62">
-        <v>-14.20257332060339</v>
+        <v>-17.16958180573633</v>
       </c>
       <c r="F62">
-        <v>0.4519571077199025</v>
+        <v>0.6067847738749497</v>
       </c>
       <c r="G62">
-        <v>-4.507153672876914</v>
+        <v>-3.275093696183323</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.358570967291254</v>
       </c>
       <c r="E63">
-        <v>-14.12107070156496</v>
+        <v>-16.6124492725672</v>
       </c>
       <c r="F63">
-        <v>0.2149777611270199</v>
+        <v>1.000663533497281</v>
       </c>
       <c r="G63">
-        <v>-4.551243927531635</v>
+        <v>-3.456075732728479</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.234090734641624</v>
       </c>
       <c r="E64">
-        <v>-13.91859749626824</v>
+        <v>-16.53388712714675</v>
       </c>
       <c r="F64">
-        <v>0.4014540322734251</v>
+        <v>0.7813085317663607</v>
       </c>
       <c r="G64">
-        <v>-5.639804327774684</v>
+        <v>-3.449979644108229</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.092298582799943</v>
       </c>
       <c r="E65">
-        <v>-14.68072423400825</v>
+        <v>-16.41216480963867</v>
       </c>
       <c r="F65">
-        <v>-0.05174660216558727</v>
+        <v>0.6687864172396871</v>
       </c>
       <c r="G65">
-        <v>-5.493975967148869</v>
+        <v>-3.348828955670136</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.938234036000344</v>
       </c>
       <c r="E66">
-        <v>-13.3345812261935</v>
+        <v>-16.00417409514414</v>
       </c>
       <c r="F66">
-        <v>-0.3285894732833904</v>
+        <v>0.5986560045512782</v>
       </c>
       <c r="G66">
-        <v>-5.787319229406358</v>
+        <v>-3.495667674452712</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.773682703604168</v>
       </c>
       <c r="E67">
-        <v>-13.47243461648721</v>
+        <v>-15.9422912464042</v>
       </c>
       <c r="F67">
-        <v>-0.02391677090113508</v>
+        <v>0.4644281789690491</v>
       </c>
       <c r="G67">
-        <v>-5.273289726862063</v>
+        <v>-3.12802523187673</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.604523378074499</v>
       </c>
       <c r="E68">
-        <v>-13.75958764748585</v>
+        <v>-16.37405494252205</v>
       </c>
       <c r="F68">
-        <v>0.408180375584157</v>
+        <v>0.6289734231263373</v>
       </c>
       <c r="G68">
-        <v>-5.001808839810557</v>
+        <v>-3.241637004248207</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.432844095255426</v>
       </c>
       <c r="E69">
-        <v>-13.52182045235075</v>
+        <v>-15.67746587948783</v>
       </c>
       <c r="F69">
-        <v>0.3731520315893772</v>
+        <v>0.96364048079656</v>
       </c>
       <c r="G69">
-        <v>-5.174274627499501</v>
+        <v>-3.213255599798214</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.260407859942184</v>
       </c>
       <c r="E70">
-        <v>-13.10844717597924</v>
+        <v>-15.56920411988352</v>
       </c>
       <c r="F70">
-        <v>0.212812408736102</v>
+        <v>0.8113964925708443</v>
       </c>
       <c r="G70">
-        <v>-5.024441384670919</v>
+        <v>-2.680353024604761</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.088495164263335</v>
       </c>
       <c r="E71">
-        <v>-13.09072542325619</v>
+        <v>-15.03671674271593</v>
       </c>
       <c r="F71">
-        <v>-0.3697203999345943</v>
+        <v>0.8130780783985274</v>
       </c>
       <c r="G71">
-        <v>-5.434296956540611</v>
+        <v>-3.111167654051911</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.9152607557115654</v>
       </c>
       <c r="E72">
-        <v>-12.48107137967329</v>
+        <v>-15.13162177469959</v>
       </c>
       <c r="F72">
-        <v>0.1356375596542861</v>
+        <v>0.6601689111483638</v>
       </c>
       <c r="G72">
-        <v>-3.904431955083318</v>
+        <v>-2.374256275019684</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.7404061044107472</v>
       </c>
       <c r="E73">
-        <v>-13.69869326304122</v>
+        <v>-15.25160804987389</v>
       </c>
       <c r="F73">
-        <v>0.02078276252132905</v>
+        <v>0.8489265061220788</v>
       </c>
       <c r="G73">
-        <v>-4.121108091678175</v>
+        <v>-2.718373298085144</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.5613691088447498</v>
       </c>
       <c r="E74">
-        <v>-14.68277592040272</v>
+        <v>-14.85957812650067</v>
       </c>
       <c r="F74">
-        <v>-0.1575962172627109</v>
+        <v>0.3322008606645808</v>
       </c>
       <c r="G74">
-        <v>-4.681540968584917</v>
+        <v>-2.499180403704455</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.3760182576021536</v>
       </c>
       <c r="E75">
-        <v>-12.35098449455701</v>
+        <v>-15.07886353124029</v>
       </c>
       <c r="F75">
-        <v>-0.01026030589858243</v>
+        <v>0.2372310230358259</v>
       </c>
       <c r="G75">
-        <v>-4.450798140133142</v>
+        <v>-2.314284861017221</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.1827733524585573</v>
       </c>
       <c r="E76">
-        <v>-14.26575612448801</v>
+        <v>-14.97610477664138</v>
       </c>
       <c r="F76">
-        <v>-0.3916920169264484</v>
+        <v>0.3760438621925502</v>
       </c>
       <c r="G76">
-        <v>-4.744230167706729</v>
+        <v>-2.295513607407116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.01934905760855425</v>
       </c>
       <c r="E77">
-        <v>-12.73773153312504</v>
+        <v>-14.89159523260377</v>
       </c>
       <c r="F77">
-        <v>-0.4495526516445911</v>
+        <v>0.2184237695226659</v>
       </c>
       <c r="G77">
-        <v>-4.349968573279757</v>
+        <v>-1.599841549936114</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.2296541799907706</v>
       </c>
       <c r="E78">
-        <v>-13.64558614983064</v>
+        <v>-15.1094602390703</v>
       </c>
       <c r="F78">
-        <v>-1.076685589649416</v>
+        <v>0.4645673446927194</v>
       </c>
       <c r="G78">
-        <v>-4.129833200101675</v>
+        <v>-1.04064616596556</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.4465500628773358</v>
       </c>
       <c r="E79">
-        <v>-13.15735954575174</v>
+        <v>-15.45813063621231</v>
       </c>
       <c r="F79">
-        <v>-0.757045116665976</v>
+        <v>-0.1994213157974607</v>
       </c>
       <c r="G79">
-        <v>-3.906434396184702</v>
+        <v>-1.442507637897263</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.6677526239294861</v>
       </c>
       <c r="E80">
-        <v>-13.54355420721357</v>
+        <v>-15.98957140412604</v>
       </c>
       <c r="F80">
-        <v>-0.6405650626887263</v>
+        <v>0.00632940807728327</v>
       </c>
       <c r="G80">
-        <v>-3.126607597563755</v>
+        <v>-1.484235168697027</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.8901207973344883</v>
       </c>
       <c r="E81">
-        <v>-14.63077771461587</v>
+        <v>-15.80256060459167</v>
       </c>
       <c r="F81">
-        <v>-0.9175413009583802</v>
+        <v>-0.27174441700108</v>
       </c>
       <c r="G81">
-        <v>-3.588124583402397</v>
+        <v>-0.8325802650321955</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.108792239694872</v>
       </c>
       <c r="E82">
-        <v>-15.27679727655897</v>
+        <v>-16.57331771546467</v>
       </c>
       <c r="F82">
-        <v>-1.066986235730036</v>
+        <v>-0.5409787335241697</v>
       </c>
       <c r="G82">
-        <v>-3.9943929922039</v>
+        <v>-0.556851696530948</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.319449130897893</v>
       </c>
       <c r="E83">
-        <v>-16.34550161466385</v>
+        <v>-17.03148337597446</v>
       </c>
       <c r="F83">
-        <v>-1.185262190236555</v>
+        <v>-0.7733208793961807</v>
       </c>
       <c r="G83">
-        <v>-2.486419084143093</v>
+        <v>-0.6931795575897016</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.516380757925031</v>
       </c>
       <c r="E84">
-        <v>-16.53199326278263</v>
+        <v>-17.45069191425735</v>
       </c>
       <c r="F84">
-        <v>-1.326116126673778</v>
+        <v>-0.8365592752932977</v>
       </c>
       <c r="G84">
-        <v>-3.223578483911476</v>
+        <v>-0.6702519985905447</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.695438744543152</v>
       </c>
       <c r="E85">
-        <v>-17.21368891000601</v>
+        <v>-18.75659030433451</v>
       </c>
       <c r="F85">
-        <v>-1.682271034772619</v>
+        <v>-0.8821733263284525</v>
       </c>
       <c r="G85">
-        <v>-2.335860054318181</v>
+        <v>-0.6944066075475248</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.852142400728054</v>
       </c>
       <c r="E86">
-        <v>-18.50910459469931</v>
+        <v>-18.5781558861859</v>
       </c>
       <c r="F86">
-        <v>-1.744604853465879</v>
+        <v>-1.252159484951838</v>
       </c>
       <c r="G86">
-        <v>-3.155521593910335</v>
+        <v>-0.3187752865227364</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.980927177216241</v>
       </c>
       <c r="E87">
-        <v>-20.55281682342093</v>
+        <v>-19.76628581593623</v>
       </c>
       <c r="F87">
-        <v>-1.625634727075814</v>
+        <v>-1.654401441872833</v>
       </c>
       <c r="G87">
-        <v>-2.833065918717342</v>
+        <v>-0.3100292921425069</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.076609504467174</v>
       </c>
       <c r="E88">
-        <v>-19.58074525321084</v>
+        <v>-20.9697120229959</v>
       </c>
       <c r="F88">
-        <v>-1.738725101640809</v>
+        <v>-1.579452416002339</v>
       </c>
       <c r="G88">
-        <v>-2.771739528272091</v>
+        <v>-0.1505232406038496</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.132687287598041</v>
       </c>
       <c r="E89">
-        <v>-22.82202766102413</v>
+        <v>-22.93097885370835</v>
       </c>
       <c r="F89">
-        <v>-2.167084654404669</v>
+        <v>-1.825525579943155</v>
       </c>
       <c r="G89">
-        <v>-2.30356514372611</v>
+        <v>-0.06069796220200586</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.143751112781868</v>
       </c>
       <c r="E90">
-        <v>-24.62554306598562</v>
+        <v>-23.65313923886954</v>
       </c>
       <c r="F90">
-        <v>-1.955792152605196</v>
+        <v>-2.286081288551624</v>
       </c>
       <c r="G90">
-        <v>-2.434614079221632</v>
+        <v>-0.1311332405256512</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.104376561503535</v>
       </c>
       <c r="E91">
-        <v>-25.4169873224676</v>
+        <v>-25.23096498722853</v>
       </c>
       <c r="F91">
-        <v>-1.535929992659253</v>
+        <v>-2.703098006468951</v>
       </c>
       <c r="G91">
-        <v>-2.579163174997801</v>
+        <v>0.04920394210549902</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.010036145634128</v>
       </c>
       <c r="E92">
-        <v>-26.72653638529929</v>
+        <v>-26.90624999253594</v>
       </c>
       <c r="F92">
-        <v>-2.788360206504298</v>
+        <v>-2.74189293704426</v>
       </c>
       <c r="G92">
-        <v>-1.99509522730771</v>
+        <v>-0.355477133984607</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.858801284651646</v>
       </c>
       <c r="E93">
-        <v>-28.66606323133193</v>
+        <v>-28.67662484773097</v>
       </c>
       <c r="F93">
-        <v>-2.760422687477482</v>
+        <v>-3.32073702567029</v>
       </c>
       <c r="G93">
-        <v>-3.434928701540461</v>
+        <v>0.1587638388715681</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.651283537057577</v>
       </c>
       <c r="E94">
-        <v>-31.0995273470151</v>
+        <v>-30.50759920936657</v>
       </c>
       <c r="F94">
-        <v>-2.521276331758876</v>
+        <v>-3.617840935093167</v>
       </c>
       <c r="G94">
-        <v>-3.259147268220803</v>
+        <v>-0.7535843551942897</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.393173448078246</v>
       </c>
       <c r="E95">
-        <v>-32.83110497861924</v>
+        <v>-33.26192589576636</v>
       </c>
       <c r="F95">
-        <v>-2.943196984700776</v>
+        <v>-4.031665125040105</v>
       </c>
       <c r="G95">
-        <v>-3.503452914823411</v>
+        <v>-0.5320209047248695</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.092656593404352</v>
       </c>
       <c r="E96">
-        <v>-36.14008057781592</v>
+        <v>-34.50696520369515</v>
       </c>
       <c r="F96">
-        <v>-3.18847077409789</v>
+        <v>-4.235004471405299</v>
       </c>
       <c r="G96">
-        <v>-3.603849098074673</v>
+        <v>-1.184425092087351</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.7650505671441927</v>
       </c>
       <c r="E97">
-        <v>-37.60186560175919</v>
+        <v>-37.49055538504246</v>
       </c>
       <c r="F97">
-        <v>-3.508461646492714</v>
+        <v>-4.835203871675501</v>
       </c>
       <c r="G97">
-        <v>-3.390770567526371</v>
+        <v>-0.9550320185891819</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.4246752841934618</v>
       </c>
       <c r="E98">
-        <v>-40.69663517366651</v>
+        <v>-39.32295637476814</v>
       </c>
       <c r="F98">
-        <v>-3.787841806965292</v>
+        <v>-5.243414215733666</v>
       </c>
       <c r="G98">
-        <v>-3.710367477392095</v>
+        <v>-1.873894020409867</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.09475509178975471</v>
       </c>
       <c r="E99">
-        <v>-41.98258153653919</v>
+        <v>-42.007741690745</v>
       </c>
       <c r="F99">
-        <v>-4.10438087239265</v>
+        <v>-5.411859413623334</v>
       </c>
       <c r="G99">
-        <v>-4.734565191230428</v>
+        <v>-1.699464952788406</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.2120749887895681</v>
       </c>
       <c r="E100">
-        <v>-45.29375833773802</v>
+        <v>-43.27544299626772</v>
       </c>
       <c r="F100">
-        <v>-4.288924562388324</v>
+        <v>-5.762232317250636</v>
       </c>
       <c r="G100">
-        <v>-4.441375962903814</v>
+        <v>-2.495199018203007</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.4634339329156856</v>
       </c>
       <c r="E101">
-        <v>-46.92210894016637</v>
+        <v>-46.37306997756652</v>
       </c>
       <c r="F101">
-        <v>-3.945587811480402</v>
+        <v>-6.121821636601484</v>
       </c>
       <c r="G101">
-        <v>-4.566555944558514</v>
+        <v>-2.707040055815121</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.6650785848964328</v>
       </c>
       <c r="E102">
-        <v>-48.91589022403809</v>
+        <v>-48.89277344980409</v>
       </c>
       <c r="F102">
-        <v>-5.036793706085983</v>
+        <v>-6.459197455678861</v>
       </c>
       <c r="G102">
-        <v>-4.978852562620898</v>
+        <v>-3.040387757442239</v>
       </c>
     </row>
   </sheetData>
